--- a/QURAN CONTENT/UPDATED OUTPUT/EN_Quran Juz Content (21-6-26).xlsx
+++ b/QURAN CONTENT/UPDATED OUTPUT/EN_Quran Juz Content (21-6-26).xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,25 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +58,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,530 +433,536 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="46" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>juz_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>language_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>contents</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 1 (Para 1) Online with Translation - One Ummah","description":"Read Quran Juz 1 (Para 1) online with Arabic text, translation, tafsir, and recitation. Juz 1 begins with Surah Al Fatihah and continues into Surah Al Baqarah, sharing guidance, faith, and the path to Allah."},"heading":{"title":"Al Quran Juz 1","description":"Read Quran Juz 1 online on One Ummah with clear Arabic text, easy translation, tafsir, and Quran recitation. Para 1 starts with Surah Al Fatihah, the opening prayer of the Quran, and continues into Surah Al Baqarah. This Juz teaches us about faith, guidance, worship, and following the straight path shown by Allah."},"searching_terms":["al quran juz 1","read quran juz 1 online","para 1 quran","read para 1 online","juz 1 arabic text","juz 1 english translation","quran para 1 translation","surah al fatihah online","surah al baqarah juz 1","juz 1 tafsir","quran juz 1 recitation"]}</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="46" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 2 (Para 2) Online with Translation - One Ummah","description":"Read Al Quran Juz 2 (Para 2) online with Arabic text, translation, tafsir &amp; quranic recitation. Learn about prayer, fasting, charity, Hajj, and Allah’s guidance in Surah Al Baqarah."},"heading":{"title":"Al Quran Juz 2","description":"Read Quran Juz 2 online with clear Arabic text and easy English translation. Juz 2 continues Surah Al Baqarah and teaches about the change of Qiblah, Ramadan fasting, prayer, charity, Hajj, family life, and staying firm in faith. Read Para 2 with tafsir and simple meaning to understand Allah’s guidance in daily life."},"searching_terms":["al quran juz 2","read para 2 online","juz 2 english translation","quran para 2 text","surah baqarah juz 2","juz 2 tafsir","read quran juz 2 online","para 2 arabic text"]}</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="46" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 3 (Para 3) Online with Translation - One Ummah","description":"Read Al Quran Juz 3 (Para 3) online with Arabic text, translation, tafsir &amp; quranic recitation. Explore key verses from Surah Al Baqarah and Surah Al Imran about faith, charity, and Allah’s guidance."},"heading":{"title":"Al Quran Juz 3","description":"Read Quran Juz 3 online with clear Arabic text and easy English translation. Juz 3 includes the final part of Surah Al Baqarah and the beginning of Surah Al Imran. This Para includes powerful verses like Ayat al Kursi and lessons about faith, giving charity, patience, and trusting Allah. Read the Holy Quran with tafsir and simple explanations on One Ummah."},"searching_terms":["al quran juz 3","read para 3 online","juz 3 english translation","quran para 3 text","surah baqarah juz 3","surah al imran online","ayat al kursi tafsir","juz 3 arabic text","read quran juz 3 online"]}</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 4 (Para 4) Online with Translation - One Ummah","description":"Read Al Quran Juz 4 (Para 4) online with Arabic text, translation, tafsir &amp; quranic recitation. Learn lessons from Surah Al Imran and the beginning of Surah An Nisa."},"heading":{"title":"Al Quran Juz 4","description":"Read Quran Juz 4 online with clear Arabic text and easy English translation. Juz 4 starts in Surah Al Imran and continues into Surah An Nisa. It shares lessons about faith, unity, giving from what we love, and staying strong after trials. It also begins important guidance about family, orphans, women, marriage, and fair rights in Islam. Read Para 4 with tafsir and simple explanations on One Ummah."},"searching_terms":["al quran juz 4","read para 4 online","quran juz 4 english translation","juz 4 arabic text","para 4 tafsir","surah al imran juz 4","surah an nisa juz 4","read quran juz 4 online"]}</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 5 (Para 5) Online with Translation - One Ummah","description":"Read Al Quran Juz 5 (Para 5) online with Arabic text, translation, tafsir &amp; quranic recitation. This Juz continues Surah An Nisa and teaches about family life, justice, faith, and good conduct."},"heading":{"title":"Al Quran Juz 5","description":"Read Quran Juz 5 online with clear Arabic text and easy English translation. Juz 5 continues Surah An Nisa, a Surah that speaks about family, marriage, justice, and the rights of people. It also reminds believers to stay sincere, follow Allah’s guidance, and treat others with fairness. Read Para 5 with tafsir, translation, and simple explanations on One Ummah."},"searching_terms":["al quran juz 5","read para 5 online","juz 5 english translation","quran para 5 text","surah an nisa juz 5","juz 5 tafsir","read quran juz 5 online","para 5 arabic text","quran juz 5 translation"]}</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 6 (Para 6) Online with Translation - One Ummah","description":"Read Al Quran Juz 6 (Para 6) online with Arabic text, translation, tafsir &amp; quranic recitation. This Juz covers the end part of Surah An Nisa and the start of Surah Al Maidah, with lessons on justice, faith, and keeping promises."},"heading":{"title":"Al Quran Juz 6","description":"Read Quran Juz 6 online with clear Arabic text and easy English translation. Juz 6 begins in Surah An Nisa and continues into Surah Al Maidah. It teaches about justice, honest speech, faith, purity, halal food, and keeping promises to Allah. Read Para 6 with tafsir, translation, and simple explanations on One Ummah."},"searching_terms":["al quran juz 6","read para 6 online","juz 6 english translation","quran para 6 arabic text","juz 6 tafsir","surah an nisa juz 6","surah al maidah online","read quran juz 6 with translation"]}</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 7 (Para 7) Online with Translation - One Ummah","description":"Read Al Quran Juz 7 (Para 7) online with Arabic text, translation, tafsir &amp; quranic recitation. Learn from Surah Al Ma'idah and Surah Al An'am about faith, truth, and the oneness of Allah."},"heading":{"title":"Al Quran Juz 7","description":"Read Quran Juz 7 online with clear Arabic text and easy English translation. Para 7 includes the final part of Surah Al Ma'idah and the beginning of Surah Al An'am. This Juz teaches about true faith, following Allah's guidance, staying away from false beliefs, and understanding the oneness of Allah. Read with tafsir and simple meanings on One Ummah."},"searching_terms":["al quran juz 7","read para 7 online","juz 7 english translation","quran juz 7 arabic text","para 7 tafsir","surah al maidah online","surah al anam translation","read quran juz 7 online"]}</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 8 (Para 8) Online with Translation - One Ummah","description":"Read Al Quran Juz 8 (Para 8) online with Arabic text, translation, tafsir &amp; quranic recitation. Learn about Allah’s signs, true faith, and lessons from past prophets."},"heading":{"title":"Al Quran Juz 8","description":"Read Quran Juz 8 online with clear Arabic text and easy English translation. Juz 8 continues Surah Al An'am and begins Surah Al A'raf. This Juz reminds us to believe in Allah alone, follow His guidance, and learn from the stories of earlier nations. Read Para 8 with tafsir, translation, and simple explanations on One Ummah."},"searching_terms":["al quran juz 8","read para 8 online","juz 8 english translation","quran para 8 arabic text","surah al anam juz 8","surah al araf online","juz 8 tafsir","read quran juz 8 online"]}</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 9 (Para 9) Online with Translation - One Ummah","description":"Read Al Quran Juz 9 (Para 9) online with Arabic text, translation, tafsir &amp; quranic recitation. Learn from Surah Al Araf and Surah Al Anfal about faith, patience, Prophet Musa, and trust in Allah."},"heading":{"title":"Al Quran Juz 9","description":"Read Quran Juz 9 online with clear Arabic text and easy English translation. Juz 9 continues Surah Al Araf and begins Surah Al Anfal. It shares lessons from the stories of past prophets, including Prophet Shuayb and Prophet Musa. This Juz teaches us to stay firm in faith, follow Allah’s guidance, and trust Him in hard times. Read Para 9 with tafsir, translation, and simple explanations on One Ummah."},"searching_terms":["al quran juz 9","read para 9 online","juz 9 english translation","quran para 9 arabic text","surah al araf juz 9","surah al anfal online","juz 9 tafsir","read quran juz 9 with translation"]}</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 10 (Para 10) Online with Translation - One Ummah","description":"Read Al Quran Juz 10 (Para 10) online with Arabic text, translation, tafsir &amp; quranic recitation. Learn lessons from Surah Al Anfal and Surah At Tawbah about faith, unity, trust in Allah, and sincere action."},"heading":{"title":"Al Quran Juz 10","description":"Read Quran Juz 10 online with clear Arabic text and easy English translation. Juz 10 includes the later part of Surah Al Anfal and the beginning of Surah At Tawbah. This para teaches about faith, unity, patience, keeping promises, and trusting Allah in hard times. Read Para 10 with tafsir, translation, and simple explanations on One Ummah."},"searching_terms":["al quran juz 10","read para 10 online","juz 10 english translation","quran para 10 arabic text","surah anfal online","surah tawbah translation","juz 10 tafsir","read quran juz 10 online"]}</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 11 (Para 11) Online with Translation - One Ummah","description":"Read Al Quran Juz 11 (Para 11) online with Arabic text, translation, tafsir &amp; quranic recitation. This Juz covers parts of Surah At Tawbah, Surah Yunus, and the start of Surah Hud, with lessons on faith, repentance, truth, and trust in Allah."},"heading":{"title":"Al Quran Juz 11","description":"Read Quran Juz 11 online with clear Arabic text and easy English translation. Juz 11 begins in Surah At Tawbah, includes all of Surah Yunus, and ends near the start of Surah Hud. This Para teaches about sincere faith, repentance, the signs of Allah, the truth of the Quran, and the need to trust Allah in every part of life. Read Para 11 with tafsir, translation, and simple guidance on One Ummah."},"searching_terms":["al quran juz 11","read para 11 online","juz 11 english translation","quran juz 11 arabic text","para 11 tafsir","surah tawbah juz 11","surah yunus online","surah hud juz 11"]}</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 12 (Para 12) Online with Translation - One Ummah","description":"Read Al Quran Juz 12 (Para 12) online with Arabic text, translation, tafsir &amp; quranic recitation. Learn from Surah Hud and Surah Yusuf about patience, faith, and trust in Allah."},"heading":{"title":"Al Quran Juz 12","description":"Read Quran Juz 12 online with clear Arabic text and easy English translation. Juz 12 begins in Surah Hud and continues into Surah Yusuf. This para teaches about the stories of past prophets, the call to worship Allah, and the need for patience during hard times. It also begins the beautiful story of Prophet Yusuf, showing trust in Allah, family trials, and hope. Read Para 12 with tafsir and simple guidance on One Ummah."},"searching_terms":["al quran juz 12","read para 12 online","juz 12 english translation","quran para 12 arabic text","surah hud juz 12","surah yusuf juz 12","juz 12 tafsir","read quran juz 12 online"]}</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 13 (Para 13) Online with Translation - One Ummah","description":"Read Al Quran Juz 13 (Para 13) online with Arabic text, translation, tafsir &amp; quranic recitation. This Juz covers lessons from Surah Yusuf, Surah Ar Rad, and Surah Ibrahim."},"heading":{"title":"Al Quran Juz 13","description":"Read Quran Juz 13 online with clear Arabic text and easy English translation. Juz 13 continues the story of Prophet Yusuf, then includes Surah Ar Rad and Surah Ibrahim. It teaches trust in Allah, patience during hardship, the power of truth, and the blessings of divine guidance. Read Para 13 with tafsir, translation, and simple explanations on One Ummah."},"searching_terms":["al quran juz 13","read para 13 online","juz 13 english translation","quran para 13 arabic text","juz 13 tafsir","surah yusuf juz 13","surah ar rad online","surah ibrahim translation"]}</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 14 (Para 14) Online with Translation - One Ummah","description":"Read Al Quran Juz 14 (Para 14) online with Arabic text, translation, tafsir &amp; recitation. Explore Surah Al Hijr and Surah An Nahl with lessons on Allah’s signs, blessings, and guidance."},"heading":{"title":"Al Quran Juz 14","description":"Read Quran Juz 14 online with clear Arabic text and easy English translation. Juz 14 includes Surah Al Hijr and Surah An Nahl. This Para teaches about Allah’s signs in creation, His many blessings, and the need to be thankful. It also reminds us to follow the Quran, stay patient, and trust Allah. Read Para 14 with tafsir, translation, and simple explanations on One Ummah."},"searching_terms":["al quran juz 14","read para 14 online","juz 14 english translation","quran para 14 text","juz 14 tafsir","surah al hijr online","surah an nahl online","read quran juz 14 arabic text","para 14 translation","quran juz 14 online"]}</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 15 (Para 15) Online with Translation - One Ummah","description":"Read Al Quran Juz 15 (Para 15) online with Arabic text, translation, tafsir &amp; quranic recitation. This Juz covers Surah Al Isra and Surah Al Kahf, with lessons on faith, guidance, patience, and Allah’s mercy."},"heading":{"title":"Al Quran Juz 15","description":"Read Quran Juz 15 online with clear Arabic text and easy English translation. Juz 15 begins with Surah Al Isra, which speaks about the Night Journey, worshiping Allah, good manners, and the Quran as guidance. It then continues into Surah Al Kahf, where we learn from the story of the People of the Cave and the lessons of patience, faith, and trust in Allah. Read Para 15 with tafsir, translation, and simple explanations on One Ummah."},"searching_terms":["al quran juz 15","read para 15 online","quran juz 15 english translation","surah isra online","surah kahf online","quran para 15 arabic text","juz 15 tafsir","read quran juz 15 online"]}</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 16 (Para 16) Online with Translation - One Ummah","description":"Read Al Quran Juz 16 (Para 16) online with Arabic text, translation, tafsir &amp; quranic recitation. Explore lessons from Surah Al Kahf, Surah Maryam, and Surah Taha."},"heading":{"title":"Al Quran Juz 16","description":"Read Quran Juz 16 online with clear Arabic text and easy English translation. Para 16 includes the ending part of Surah Al Kahf, all of Surah Maryam, and Surah Taha. This Juz shares powerful lessons about patience, trust in Allah, the story of Maryam and Isa, and the life of Prophet Musa. Read with tafsir and simple meanings on One Ummah."},"searching_terms":["al quran juz 16","read para 16 online","juz 16 english translation","quran para 16 arabic text","juz 16 tafsir","surah kahf juz 16","surah maryam online","surah taha translation","read quran juz 16 online"]}</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 17 (Para 17) Online with Translation - One Ummah","description":"Read Al Quran Juz 17 (Para 17) online with Arabic text, translation, tafsir &amp; recitation. This Juz includes Surah Al Anbiya and Surah Al Hajj, with lessons about the prophets, faith, worship, and Hajj."},"heading":{"title":"Al Quran Juz 17","description":"Read Quran Juz 17 online with clear Arabic text and easy English translation. Juz 17 includes Surah Al Anbiya and Surah Al Hajj. It shares stories of the prophets, reminds us about the Day of Judgment, and teaches the value of worship, prayer, sacrifice, and Hajj. Explore Para 17 with tafsir and simple meaning on One Ummah."},"searching_terms":["al quran juz 17","read para 17 online","juz 17 english translation","quran juz 17 arabic text","surah al anbiya online","surah al hajj translation","para 17 tafsir","read quran juz 17 online"]}</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 18 (Para 18) Online with Translation - One Ummah","description":"Read Al Quran Juz 18 (Para 18) online with Arabic text, translation, tafsir &amp; quranic recitation. Learn about true believers, modesty, family rules, and the light of Allah."},"heading":{"title":"Al Quran Juz 18","description":"Read Quran Juz 18 online with clear Arabic text and easy English translation. Juz 18 begins with Surah Al Mu'minun, includes Surah An Nur, and continues into Surah Al Furqan. This para teaches about the qualities of true believers, the signs of Allah, modesty, family life, and guidance for a clean and faithful society. Read Para 18 with tafsir, translation, and simple explanations on One Ummah."},"searching_terms":["al quran juz 18","read para 18 online","juz 18 english translation","quran para 18 text","surah al muminun online","surah an nur translation","juz 18 tafsir","read quran juz 18 arabic text","para 18 quran with translation"]}</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 19 (Para 19) Online with Translation - One Ummah","description":"Read Al Quran Juz 19 (Para 19) online with Arabic text, translation, tafsir &amp; quranic recitation. Explore Surah Al Furqan, Ash Shuara, and An Naml with lessons on faith, patience, and the stories of the prophets."},"heading":{"title":"Al Quran Juz 19","description":"Read Quran Juz 19 online with clear Arabic text and easy English translation. Para 19 begins in Surah Al Furqan, includes all of Surah Ash Shuara, and continues into Surah An Naml. This Juz shares powerful lessons about true faith, patience, the signs of Allah, and the stories of many prophets. Read Al Quran Juz 19 with tafsir and simple meaning on One Ummah."},"searching_terms":["al quran juz 19","read quran juz 19 online","para 19 online","juz 19 english translation","quran para 19 arabic text","juz 19 tafsir","surah al furqan juz 19","surah ash shuara online","surah an naml translation"]}</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="21" ht="46" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 20 (Para 20) Online with Translation - One Ummah","description":"Read Al Quran Juz 20 (Para 20) online with Arabic text, translation, tafsir &amp; quranic recitation. Learn from the stories of Prophet Musa, Qarun, and the tests of faith."},"heading":{"title":"Al Quran Juz 20","description":"Read Quran Juz 20 online with clear Arabic text and easy English translation. Juz 20 includes parts of Surah An Naml, Surah Al Qasas, and Surah Al Ankabut. This Para shares powerful lessons from the story of Prophet Musa, the pride of Qarun, and the need to stay strong during tests of faith. Read the Holy Quran with tafsir and simple explanations on One Ummah."},"searching_terms":["al quran juz 20","read para 20 online","juz 20 english translation","quran para 20 text","juz 20 tafsir","surah al qasas online","surah al ankabut translation","read quran juz 20 arabic text"]}</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="22" ht="46" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 21 (Para 21) Online with Translation - One Ummah","description":"Read Al Quran Juz 21 (Para 21) online with Arabic text, translation, tafsir &amp; quranic recitation. Explore Surah Al Ankabut, Ar Rum, Luqman, As Sajdah, and Al Ahzab."},"heading":{"title":"Al Quran Juz 21","description":"Read Quran Juz 21 online with clear Arabic text and easy English translation. Juz 21 includes parts of Surah Al Ankabut, Surah Ar Rum, Surah Luqman, Surah As Sajdah, and Surah Al Ahzab. This Para teaches about strong faith, Allah’s signs in creation, wise advice from Luqman, prayer, patience, and guidance for the Muslim community. Read the Holy Quran with tafsir and simple explanations on One Ummah."},"searching_terms":["al quran juz 21","read para 21 online","juz 21 english translation","quran juz 21 arabic text","para 21 tafsir","surah rum online","surah luqman translation","surah sajdah online","read quran juz 21 with translation"]}</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="23" ht="46" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 22 (Para 22) Online with Translation - One Ummah","description":"Read Al Quran Juz 22 (Para 22) online with Arabic text, translation, tafsir &amp; quranic recitation. Learn from Surah Al Ahzab, Saba, Fatir, and the start of Surah Yasin about faith, gratitude, modesty, and the power of Allah."},"heading":{"title":"Al Quran Juz 22","description":"Read Quran Juz 22 online with clear Arabic text and easy English translation. Para 22 begins in Surah Al Ahzab and includes Surah Saba, Surah Fatir, and the beginning of Surah Yasin. This Juz teaches about respect for the Prophet, family values, modesty, being thankful to Allah, and believing in the Hereafter. Read with tafsir and simple meaning on One Ummah."},"searching_terms":["al quran juz 22","read para 22 online","juz 22 english translation","quran para 22 arabic text","juz 22 tafsir","surah ahzab juz 22","surah saba online","surah fatir translation","surah yasin beginning","read quran juz 22 online"]}</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="24" ht="46" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 23 (Para 23) Online with Translation - One Ummah","description":"Read Al Quran Juz 23 (Para 23) online with Arabic text, translation, tafsir &amp; quranic recitation. Explore Surah Ya-Sin, As-Saffat, Sad, and Az-Zumar with lessons on faith, resurrection, and sincere worship."},"heading":{"title":"Al Quran Juz 23","description":"Read Quran Juz 23 online with clear Arabic text and easy English translation. Para 23 includes parts of Surah Ya-Sin, Surah As-Saffat, Surah Sad, and Surah Az-Zumar. This Juz reminds us about life after death, the power of Allah, the stories of the prophets, and the need to worship Allah with a sincere heart. Read with tafsir and simple meaning on One Ummah."},"searching_terms":["al quran juz 23","read para 23 online","juz 23 english translation","quran juz 23 arabic text","juz 23 tafsir","surah yasin juz 23","surah as saffat online","surah sad translation","surah az zumar para 23"]}</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="25" ht="46" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 24 (Para 24) Online with Translation - One Ummah","description":"Read Al Quran Juz 24 (Para 24) online with Arabic text, translation, tafsir &amp; quranic recitation. Learn about sincere faith, Allah’s mercy, and the clear signs of the Quran."},"heading":{"title":"Al Quran Juz 24","description":"Read Quran Juz 24 online with clear Arabic text and easy English translation. Juz 24 includes parts of Surah Az Zumar, Surah Ghafir, and Surah Fussilat. This Juz reminds us to worship Allah alone, turn back to Him with hope, and trust His mercy. It also speaks about the Day of Judgment, the story of a believing man from Pharaoh’s people, and the clear signs of Allah in the Quran and creation. Read Para 24 with tafsir and simple explanations on One Ummah."},"searching_terms":["al quran juz 24","read para 24 online","juz 24 english translation","quran para 24 arabic text","juz 24 tafsir","surah az zumar online","surah ghafir translation","surah fussilat tafsir","read quran juz 24 online"]}</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="26" ht="46" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 25 (Para 25) Online with Translation - One Ummah","description":"Read Al Quran Juz 25 (Para 25) online with Arabic text, translation, tafsir &amp; quranic recitation. Learn about Allah’s signs, revelation, faith, and the Day of Judgment."},"heading":{"title":"Al Quran Juz 25","description":"Read Quran Juz 25 online with clear Arabic text and easy English translation. Juz 25 includes parts of Surah Fussilat and full Surahs Ash Shura, Az Zukhruf, Ad Dukhan, and Al Jathiyah. This Para teaches us about Allah’s power, the truth of the Quran, the signs in creation, and the final return to Allah. Read Para 25 with tafsir and simple meaning on One Ummah."},"searching_terms":["al quran juz 25","read para 25 online","juz 25 english translation","quran para 25 arabic text","juz 25 tafsir","surah ash shura online","surah az zukhruf translation","surah ad dukhan tafsir","surah al jathiyah online"]}</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="27" ht="46" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 26 (Para 26) Online with Translation - One Ummah","description":"Read Al Quran Juz 26 (Para 26) online with Arabic text, translation, tafsir &amp; quranic recitation. Explore Surah Al Ahqaf, Muhammad, Al Fath, Al Hujurat, Qaf, and Adh Dhariyat."},"heading":{"title":"Al Quran Juz 26","description":"Read Quran Juz 26 online with clear Arabic text and easy English translation. Para 26 includes Surah Al Ahqaf, Surah Muhammad, Surah Al Fath, Surah Al Hujurat, Surah Qaf, and the beginning of Surah Adh Dhariyat. This juz talks about faith in Allah, good manners, unity among believers, the victory given by Allah, and the truth of the Day of Judgment. Read with tafsir and simple meaning on One Ummah."},"searching_terms":["al quran juz 26","read quran juz 26 online","read para 26 online","juz 26 english translation","quran para 26 arabic text","juz 26 tafsir","surah al ahqaf online","surah muhammad online","surah al fath online","surah al hujurat online","surah qaf online","para 26 quran recitation"]}</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="28" ht="46" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 27 (Para 27) Online with Translation - One Ummah","description":"Read Al Quran Juz 27 (Para 27) online with Arabic text, translation, tafsir &amp; quranic recitation. Explore Surah Ar Rahman, Al Waqiah, and Al Hadid with lessons on Allah’s mercy, the Hereafter, and true faith."},"heading":{"title":"Al Quran Juz 27","description":"Read Quran Juz 27 online with clear Arabic text and easy English translation. Para 27 includes parts of Surah Adh Dhariyat and Surah At Tur, then continues with Surah An Najm, Al Qamar, Ar Rahman, Al Waqiah, and Al Hadid. This Juz reminds us about Allah’s power, His mercy, the Day of Judgment, and the reward of true believers. Read with tafsir and simple meaning on One Ummah."},"searching_terms":["al quran juz 27","read para 27 online","juz 27 english translation","quran para 27 arabic text","juz 27 tafsir","surah rahman online","surah waqiah translation","surah hadid tafsir"]}</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="29" ht="46" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 28 (Para 28) Online with Translation - One Ummah","description":"Read Al Quran Juz 28 (Para 28) online with Arabic text, translation, tafsir &amp; quranic recitation. Explore Surahs Al Mujadilah to At Tahrim, covering faith, family life, manners, and trust in Allah."},"heading":{"title":"Al Quran Juz 28","description":"Read Quran Juz 28 online with clear Arabic text and easy English translation. Juz 28 includes Surah Al Mujadilah, Al Hashr, Al Mumtahanah, As Saff, Al Jumuah, Al Munafiqun, At Taghabun, At Talaq, and At Tahrim. This Para teaches about strong faith, good manners, family rules, unity, charity, and trusting Allah in every part of life. Read Para 28 with tafsir and simple explanations on One Ummah."},"searching_terms":["al quran juz 28","read para 28 online","juz 28 english translation","quran para 28 text","juz 28 arabic text","juz 28 tafsir","surah al mujadilah online","surah al hashr translation","surah al jumuah online","surah at talaq tafsir"]}</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="30" ht="46" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 29 (Para 29) Online with Translation - One Ummah","description":"Read Al Quran Juz 29 (Para 29) online with Arabic text, translation, tafsir &amp; quranic recitation. Explore Surah Al Mulk to Surah Al Mursalat, with reminders about Allah’s power, the Hereafter, and the Day of Judgment."},"heading":{"title":"Al Quran Juz 29","description":"Read Quran Juz 29 online with clear Arabic text and easy English translation. Juz 29 starts with Surah Al Mulk and continues through Surah Al Mursalat. This Para reminds us about Allah’s great power, life after death, the truth of the Quran, and the Day of Judgment. Read Para 29 with tafsir, translation, and simple explanations on One Ummah."},"searching_terms":["al quran juz 29","read para 29 online","juz 29 english translation","surah al mulk online","quran para 29 text","juz 29 tafsir","read quran juz 29","para 29 arabic text","juz 29 with translation"]}</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="31" ht="46" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"Read Al Quran Juz 30 (Para 30) Online with Translation - One Ummah","description":"Read Al Quran Juz 30 (Para 30) online with Arabic text, translation, tafsir &amp; quranic recitation. Learn short Surahs about the Hereafter, faith, and Allah's protection."},"heading":{"title":"Al Quran Juz 30","description":"Read Quran Juz 30 online with clear Arabic text and easy English translation. Juz 30 starts with Surah An Naba and ends with Surah An Nas. This Para includes many short Surahs that talk about the Day of Judgment, faith in Allah, good deeds, prayer, and seeking Allah's protection. Read Para 30 with tafsir and simple meaning on One Ummah."},"searching_terms":["al quran juz 30","read para 30 online","juz 30 english translation","quran para 30 text","juz amma online","surah naba to surah nas","para 30 arabic text","juz 30 tafsir","short surahs of quran"]}</t>
         </is>
